--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487460_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487460_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8959</v>
+        <v>6.5217</v>
       </c>
       <c r="E2" t="n">
         <v>3.0475</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8484</v>
+        <v>3.4742</v>
       </c>
       <c r="G2" t="n">
         <v>2.4434</v>
@@ -610,13 +610,13 @@
         <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4698</v>
+        <v>0.0956</v>
       </c>
       <c r="T2" t="n">
         <v>-0.6246</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0944</v>
+        <v>0.7202</v>
       </c>
       <c r="V2" t="n">
         <v>3.9828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8374</v>
+        <v>5.0826</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4257</v>
+        <v>3.3234</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4117</v>
+        <v>1.7592</v>
       </c>
       <c r="G3" t="n">
         <v>2.3972</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5758</v>
+        <v>-0.3307</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5058</v>
+        <v>-0.6081</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.2775</v>
       </c>
       <c r="V3" t="n">
         <v>0.6659</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4393</v>
+        <v>3.6836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1991</v>
+        <v>0.7108</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2402</v>
+        <v>2.9729</v>
       </c>
       <c r="G4" t="n">
         <v>2.762</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2441</v>
+        <v>0.4884</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6534</v>
+        <v>-0.1417</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8975</v>
+        <v>0.6302</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1143</v>
+        <v>2.8759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7644</v>
+        <v>0.3121</v>
       </c>
       <c r="F5" t="n">
-        <v>2.35</v>
+        <v>2.5638</v>
       </c>
       <c r="G5" t="n">
         <v>1.0627</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.486</v>
+        <v>0.2476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1062</v>
+        <v>0.1076</v>
       </c>
       <c r="V5" t="n">
         <v>0.3905</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DOMINGUEZ ITURZA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6032</v>
+        <v>1.8061</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0649</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6681</v>
+        <v>1.8748</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2971</v>
+        <v>2.9847</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7312</v>
+        <v>-1.3957</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5658</v>
+        <v>4.3804</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8096</v>
+        <v>2.016</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2698</v>
+        <v>-1.9446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5399</v>
+        <v>3.9607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5125999999999999</v>
+        <v>0.9686</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5385</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.026</v>
+        <v>0.4197</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5668</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8142</v>
+        <v>0.3295</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6246</v>
+        <v>-0.0306</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4388</v>
+        <v>0.3601</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9412</v>
+        <v>-0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. DOMINGUEZ ITURZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5596</v>
+        <v>1.1547</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.128</v>
+        <v>-1.0055</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6876</v>
+        <v>2.1602</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9847</v>
+        <v>3.2971</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3957</v>
+        <v>2.7312</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3804</v>
+        <v>0.5658</v>
       </c>
       <c r="J7" t="n">
-        <v>2.016</v>
+        <v>3.8096</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9446</v>
+        <v>3.2698</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9607</v>
+        <v>0.5399</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9686</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5489000000000001</v>
+        <v>-0.5385</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4197</v>
+        <v>0.026</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1751</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7626</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>0.083</v>
+        <v>0.3657</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.09</v>
+        <v>-0.5652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.173</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="V7" t="n">
+        <v>-0.9412</v>
+      </c>
+      <c r="W7" t="n">
         <v>-0.3329</v>
       </c>
-      <c r="W7" t="n">
-        <v>0.8837</v>
-      </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1276</v>
+        <v>0.6171</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7894</v>
+        <v>-1.3801</v>
       </c>
       <c r="F8" t="n">
-        <v>1.917</v>
+        <v>1.9972</v>
       </c>
       <c r="G8" t="n">
         <v>2.6988</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4329</v>
+        <v>0.0566</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.188</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7551</v>
+        <v>0.8353</v>
       </c>
       <c r="V8" t="n">
         <v>-1.159</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CACHON VILLAMEDIANA</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6871</v>
+        <v>-1.8797</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0196</v>
+        <v>-1.0168</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6675</v>
+        <v>-0.8629</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1691</v>
+        <v>-0.7937</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2354</v>
+        <v>-0.4352</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4045</v>
+        <v>-0.3585</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2233</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1021</v>
+        <v>0.0408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1212</v>
+        <v>0.0404</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0542</v>
+        <v>-0.875</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3375</v>
+        <v>-0.476</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2833</v>
+        <v>-0.399</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5758</v>
+        <v>-0.3026</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1476</v>
+        <v>-0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4282</v>
+        <v>-0.1838</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8237</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>R. CACHON VILLAMEDIANA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9332</v>
+        <v>-1.9125</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0168</v>
+        <v>-0.1649</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9164</v>
+        <v>-1.7477</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7937</v>
+        <v>0.1691</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4352</v>
+        <v>-0.2354</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3585</v>
+        <v>0.4045</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.2233</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0408</v>
+        <v>0.1021</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0404</v>
+        <v>0.1212</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.875</v>
+        <v>-0.0542</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.476</v>
+        <v>-0.3375</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.399</v>
+        <v>0.2833</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3561</v>
+        <v>0.3504</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>0.0023</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2373</v>
+        <v>0.348</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.8237</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9363</v>
+        <v>-3.6318</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8518</v>
+        <v>-6.8947</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9155</v>
+        <v>3.263</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4595</v>
@@ -1312,13 +1312,13 @@
         <v>2.3502</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8905</v>
+        <v>-0.5859</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7269</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2065</v>
+        <v>0.141</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9988</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.0207</v>
+        <v>14.3177</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4338</v>
+        <v>-3.1368</v>
       </c>
       <c r="F12" t="n">
-        <v>17.4546</v>
+        <v>17.4547</v>
       </c>
       <c r="G12" t="n">
         <v>15.5618</v>
@@ -1390,10 +1390,10 @@
         <v>16.6471</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4176000000000001</v>
+        <v>0.7146</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.7494</v>
+        <v>-3.4523</v>
       </c>
       <c r="U12" t="n">
         <v>4.167</v>
@@ -1405,7 +1405,7 @@
         <v>5.244499999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.2444</v>
+        <v>-5.244400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2366</v>
+        <v>2.3774</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7877</v>
+        <v>0.276</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4489</v>
+        <v>2.1014</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3314</v>
@@ -1468,13 +1468,13 @@
         <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5904</v>
+        <v>0.7312</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5264</v>
+        <v>0.0147</v>
       </c>
       <c r="U13" t="n">
-        <v>1.064</v>
+        <v>0.7165</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1767</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3239</v>
+        <v>1.3774</v>
       </c>
       <c r="E14" t="n">
         <v>-0.48</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8039</v>
+        <v>1.8574</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3172</v>
@@ -1546,13 +1546,13 @@
         <v>3.3294</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3031</v>
+        <v>-0.2497</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7675</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4644</v>
+        <v>0.5179</v>
       </c>
       <c r="V14" t="n">
         <v>2.5318</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3214</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E15" t="n">
         <v>1.8253</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5039</v>
+        <v>-1.2633</v>
       </c>
       <c r="G15" t="n">
         <v>0.5046</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7483</v>
+        <v>-0.5077</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4993</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.249</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3933</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2455</v>
+        <v>0.4418</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4184</v>
+        <v>-1.623</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6639</v>
+        <v>2.0648</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5385</v>
@@ -1702,13 +1702,13 @@
         <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6061</v>
+        <v>-0.4098</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4111</v>
+        <v>-0.6158</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.195</v>
+        <v>0.206</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1767</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1172</v>
+        <v>-0.2649</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5628</v>
+        <v>0.0204</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4456</v>
+        <v>-0.2853</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9836</v>
+        <v>-0.3837</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5975</v>
+        <v>0.0204</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.581</v>
+        <v>-0.4042</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4133</v>
+        <v>0.0204</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9339</v>
+        <v>0.0204</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5206</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3969</v>
+        <v>-0.4042</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3364</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0604</v>
+        <v>-0.4042</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0536</v>
+        <v>0.1188</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5476</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4939</v>
+        <v>0.1188</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8426</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.158</v>
+        <v>-0.5311</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0204</v>
+        <v>-0.8698</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1784</v>
+        <v>0.3387</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3837</v>
+        <v>-0.9836</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0204</v>
+        <v>0.5975</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>-1.581</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0204</v>
+        <v>0.4133</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0204</v>
+        <v>0.9339</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5206</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4042</v>
+        <v>-1.3969</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.3364</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4042</v>
+        <v>-1.0604</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2257</v>
+        <v>-0.4676</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.8546</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2257</v>
+        <v>0.387</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.8426</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.3933</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2422</v>
+        <v>-0.9573</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4842</v>
+        <v>-1.2795</v>
       </c>
       <c r="F19" t="n">
-        <v>0.242</v>
+        <v>0.3222</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4497</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1841</v>
+        <v>0.1007</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1606</v>
+        <v>0.0441</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0236</v>
+        <v>0.0566</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3202</v>
+        <v>-1.77</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1528</v>
+        <v>-2.2551</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8326</v>
+        <v>0.4851</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9972</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8729</v>
+        <v>0.423</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1653</v>
+        <v>0.0629</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7076</v>
+        <v>0.3601</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.185</v>
+        <v>-2.0292</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4157</v>
+        <v>0.518</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6007</v>
+        <v>-2.5472</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8258</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3384</v>
+        <v>-0.1826</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3349</v>
+        <v>-4.2232</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1288</v>
+        <v>-5.9071</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2061</v>
+        <v>1.6839</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1229</v>
+        <v>-3.0656</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.1029</v>
+        <v>-2.96</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.02</v>
+        <v>-0.1057</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3177</v>
+        <v>-1.3938</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3581</v>
+        <v>-2.0809</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0404</v>
+        <v>0.6871</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8052</v>
+        <v>-1.6718</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7447</v>
+        <v>-0.8791</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0604</v>
+        <v>-0.7927</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5875</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2904</v>
+        <v>0.1926</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0692</v>
+        <v>-0.5387</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7789</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="V22" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.6659</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2166</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-0.5507</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8907</v>
+        <v>-4.2685</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.5211</v>
+        <v>-3.8218</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6304</v>
+        <v>-0.4466</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0656</v>
+        <v>-4.1229</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.96</v>
+        <v>-3.1029</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1057</v>
+        <v>-1.02</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3938</v>
+        <v>-2.3177</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0809</v>
+        <v>-2.3581</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6871</v>
+        <v>0.0404</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6718</v>
+        <v>-1.8052</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8791</v>
+        <v>-0.7447</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7927</v>
+        <v>-1.0604</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.5875</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.9585</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4749</v>
+        <v>-0.2239</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1528</v>
+        <v>-0.7622</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5383</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6083</v>
+        <v>0.6659</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0576</v>
+        <v>1.2166</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6659</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9</v>
+        <v>-4.7351</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7556</v>
+        <v>-3.8579</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1445</v>
+        <v>-0.8772</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0505</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1076</v>
+        <v>0.0573</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0129</v>
+        <v>-0.1153</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1726</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.0208</v>
+        <v>-14.0207</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.4546</v>
+        <v>-17.4545</v>
       </c>
       <c r="F25" t="n">
-        <v>3.433700000000001</v>
+        <v>3.4339</v>
       </c>
       <c r="G25" t="n">
         <v>-15.5615</v>
@@ -2380,7 +2380,7 @@
         <v>-1.8847</v>
       </c>
       <c r="K25" t="n">
-        <v>2.338299999999999</v>
+        <v>2.3383</v>
       </c>
       <c r="L25" t="n">
         <v>-4.223299999999999</v>
@@ -2404,13 +2404,13 @@
         <v>18.6055</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4174999999999999</v>
+        <v>-0.4177000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.1669</v>
+        <v>-4.167000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.7493</v>
+        <v>3.7495</v>
       </c>
       <c r="V25" t="n">
         <v>0.000100000000000211</v>
